--- a/feedback_forms/005_transportation_service_release_industry_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/005_transportation_service_release_industry_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>transport_service_release_feedback</t>
+          <t>service_release_feedback</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -551,10 +551,14 @@
           <t>Release Date</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide the release date of the service</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,76 +581,80 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>release_notes</t>
+          <t>release_partners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Release Notes</t>
+          <t>Partners Involved</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>release_partners</t>
+          <t>release_clients</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Partners</t>
+          <t>Clients Affected</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>release_clients</t>
+          <t>satisfaction_score</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Clients</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Satisfaction Score</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide a score between 1-5</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +666,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>satisfaction_score</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Satisfaction Score</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +689,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>release_notes_2</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Additional Release Notes</t>
+          <t>Email Contact</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,156 +712,160 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>release_date_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Release Date Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>release_notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Release Notes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>release_date_time</t>
+          <t>partner_affected</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Release Date Time</t>
+          <t>Partner Affected</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>release_notes_3</t>
+          <t>client_affected</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Release Notes</t>
+          <t>Client Affected</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>release_partners_2</t>
+          <t>satisfaction_score_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Partners</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Satisfaction Score 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please provide a score between 1-5</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>release_clients_2</t>
+          <t>feedback_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Clients</t>
+          <t>Feedback 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +877,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>satisfaction_score_2</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Satisfaction Score</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,202 +900,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>feedback_2</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email_2</t>
+          <t>release_date_time_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Release Date Time 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>phone_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>release_date_time_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Release Date Time</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>release_notes_3_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Release Notes</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>release_partners_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Partners</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>release_clients_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Clients</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>satisfaction_score_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Satisfaction Score</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>feedback_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Feedback</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +949,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1228,7 +1079,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>release_partners_2_choices</t>
+          <t>partner_affected_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1096,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>release_partners_2_choices</t>
+          <t>partner_affected_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1113,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>release_partners_2_choices</t>
+          <t>partner_affected_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1130,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>release_clients_2_choices</t>
+          <t>client_affected_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1147,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>release_clients_2_choices</t>
+          <t>client_affected_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1164,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>release_clients_2_choices</t>
+          <t>client_affected_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1322,108 +1173,6 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>Client 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>release_partners_3_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>partner_1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Partner 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>release_partners_3_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>partner_2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Partner 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>release_partners_3_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>partner_3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Partner 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>release_clients_3_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>client_1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Client 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>release_clients_3_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>client_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Client 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>release_clients_3_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>client_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>Client 3</t>
         </is>
